--- a/site/public/ig/StructureDefinition-heartland-patient.xlsx
+++ b/site/public/ig/StructureDefinition-heartland-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T20:13:50-04:00</t>
+    <t>2026-09-17T14:02:25-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/public/ig/StructureDefinition-heartland-patient.xlsx
+++ b/site/public/ig/StructureDefinition-heartland-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T14:02:25-04:00</t>
+    <t>2026-09-17T14:11:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
